--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RiskLevelImport001.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RiskLevelImport001.xlsx
@@ -21,15 +21,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>资产类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>资产名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>风险五级分类</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产代码</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -389,13 +389,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -407,7 +407,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1336">
       <formula1>"01 关注,02 次级,03 可疑,04 损失,05 正常"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1490">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1413:A1490">
       <formula1>"F01 债券,F07 存款类资产,F17 计划类资产（利率型）,F18 项目类资产 "</formula1>
     </dataValidation>
   </dataValidations>
